--- a/artfynd/A 38819-2024 artfynd.xlsx
+++ b/artfynd/A 38819-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119820377</v>
+        <v>119820376</v>
       </c>
       <c r="B2" t="n">
-        <v>79115</v>
+        <v>78263</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -722,7 +722,7 @@
         <v>411531</v>
       </c>
       <c r="R2" t="n">
-        <v>6809862</v>
+        <v>6809867</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119820380</v>
+        <v>119820377</v>
       </c>
       <c r="B3" t="n">
-        <v>78262</v>
+        <v>79115</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>411532</v>
+        <v>411531</v>
       </c>
       <c r="R3" t="n">
-        <v>6809863</v>
+        <v>6809862</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119820376</v>
+        <v>119820380</v>
       </c>
       <c r="B4" t="n">
-        <v>78263</v>
+        <v>78262</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>411531</v>
+        <v>411532</v>
       </c>
       <c r="R4" t="n">
-        <v>6809867</v>
+        <v>6809863</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 38819-2024 artfynd.xlsx
+++ b/artfynd/A 38819-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119820376</v>
+        <v>119820381</v>
       </c>
       <c r="B2" t="n">
-        <v>78263</v>
+        <v>78171</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>411531</v>
+        <v>411501</v>
       </c>
       <c r="R2" t="n">
-        <v>6809867</v>
+        <v>6809842</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119820377</v>
+        <v>119820376</v>
       </c>
       <c r="B3" t="n">
-        <v>79115</v>
+        <v>78263</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -833,7 +833,7 @@
         <v>411531</v>
       </c>
       <c r="R3" t="n">
-        <v>6809862</v>
+        <v>6809867</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119820380</v>
+        <v>119820377</v>
       </c>
       <c r="B4" t="n">
-        <v>78262</v>
+        <v>79115</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>411532</v>
+        <v>411531</v>
       </c>
       <c r="R4" t="n">
-        <v>6809863</v>
+        <v>6809862</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119820381</v>
+        <v>119820380</v>
       </c>
       <c r="B5" t="n">
-        <v>78171</v>
+        <v>78262</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>411501</v>
+        <v>411532</v>
       </c>
       <c r="R5" t="n">
-        <v>6809842</v>
+        <v>6809863</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 38819-2024 artfynd.xlsx
+++ b/artfynd/A 38819-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119820381</v>
+        <v>119820376</v>
       </c>
       <c r="B2" t="n">
-        <v>78171</v>
+        <v>78279</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>411501</v>
+        <v>411531</v>
       </c>
       <c r="R2" t="n">
-        <v>6809842</v>
+        <v>6809867</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119820376</v>
+        <v>119820377</v>
       </c>
       <c r="B3" t="n">
-        <v>78263</v>
+        <v>79131</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -833,7 +833,7 @@
         <v>411531</v>
       </c>
       <c r="R3" t="n">
-        <v>6809867</v>
+        <v>6809862</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119820377</v>
+        <v>119820380</v>
       </c>
       <c r="B4" t="n">
-        <v>79115</v>
+        <v>78278</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>411531</v>
+        <v>411532</v>
       </c>
       <c r="R4" t="n">
-        <v>6809862</v>
+        <v>6809863</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119820380</v>
+        <v>119820381</v>
       </c>
       <c r="B5" t="n">
-        <v>78262</v>
+        <v>78187</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>411532</v>
+        <v>411501</v>
       </c>
       <c r="R5" t="n">
-        <v>6809863</v>
+        <v>6809842</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 38819-2024 artfynd.xlsx
+++ b/artfynd/A 38819-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119820376</v>
+        <v>119820377</v>
       </c>
       <c r="B2" t="n">
-        <v>78279</v>
+        <v>79131</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -722,7 +722,7 @@
         <v>411531</v>
       </c>
       <c r="R2" t="n">
-        <v>6809867</v>
+        <v>6809862</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119820377</v>
+        <v>119820376</v>
       </c>
       <c r="B3" t="n">
-        <v>79131</v>
+        <v>78279</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -833,7 +833,7 @@
         <v>411531</v>
       </c>
       <c r="R3" t="n">
-        <v>6809862</v>
+        <v>6809867</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 38819-2024 artfynd.xlsx
+++ b/artfynd/A 38819-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119820377</v>
+        <v>119820381</v>
       </c>
       <c r="B2" t="n">
-        <v>79131</v>
+        <v>78187</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>411531</v>
+        <v>411501</v>
       </c>
       <c r="R2" t="n">
-        <v>6809862</v>
+        <v>6809842</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119820376</v>
+        <v>119820377</v>
       </c>
       <c r="B3" t="n">
-        <v>78279</v>
+        <v>79131</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -833,7 +833,7 @@
         <v>411531</v>
       </c>
       <c r="R3" t="n">
-        <v>6809867</v>
+        <v>6809862</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119820381</v>
+        <v>119820376</v>
       </c>
       <c r="B5" t="n">
-        <v>78187</v>
+        <v>78279</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>411501</v>
+        <v>411531</v>
       </c>
       <c r="R5" t="n">
-        <v>6809842</v>
+        <v>6809867</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 38819-2024 artfynd.xlsx
+++ b/artfynd/A 38819-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119820381</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119820380</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119820376</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,8 +1116,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119820377</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>